--- a/out/27S/ver1/27S_ver1_instructor.xlsx
+++ b/out/27S/ver1/27S_ver1_instructor.xlsx
@@ -84,7 +84,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +129,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE6F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6FFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -186,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -217,6 +222,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1007,13 +1015,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -1024,26 +1026,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Corley 267
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Corley 267
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Corley 267
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -1055,7 +1057,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="4" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -1066,11 +1068,29 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Corley 267
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Corley 267
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Corley 267
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1078,11 +1098,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1114,26 +1134,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1141,11 +1146,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1153,21 +1158,21 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>STAT 2163-004
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>STAT 2163-004
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>STAT 2163-004
 2:00 PM-2:50 PM</t>
@@ -1248,18 +1253,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="F15:F16"/>
-    <mergeCell ref="F13:F14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C6:C8"/>
     <mergeCell ref="B15:B16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1366,7 +1370,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -1377,11 +1387,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1389,11 +1417,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1401,29 +1429,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 0803-004
-11:00 AM-11:50 AM
-/ MATH 1003-004</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 0803-004
-11:00 AM-11:50 AM
-/ MATH 1003-004</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 0803-004
-11:00 AM-11:50 AM
-/ MATH 1003-004</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1431,11 +1441,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1559,11 +1569,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="4">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C6:C8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -1632,11 +1643,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2033-001
+Corley 102
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2033-001
+Corley 102
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2033-001
+Corley 102
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1644,11 +1673,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1687,21 +1716,9 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Corley 104
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Corley 104
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1710,29 +1727,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2033-001
-Corley 102
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2033-001
-Corley 102
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2033-001
-Corley 102
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1740,11 +1739,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1849,9 +1848,21 @@
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Corley 102
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Corley 102
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1861,9 +1872,9 @@
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
+      <c r="E17" s="8" t="n"/>
       <c r="F17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1873,9 +1884,9 @@
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
+      <c r="E18" s="6" t="n"/>
       <c r="F18" s="4" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1918,15 +1929,15 @@
   <autoFilter ref="A2:F20"/>
   <mergeCells count="12">
     <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -1997,41 +2008,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 0903-002
-Corley 104
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-002
-Corley 104
-8:00 AM-9:20 AM</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 0903-002
-Corley 104
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-002
-Corley 104
-8:00 AM-9:20 AM</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 0903-002
-Corley 104
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2039,11 +2020,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2058,7 +2039,7 @@
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>MATH 1003-001
@@ -2066,7 +2047,7 @@
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
+      <c r="E5" s="4" t="n"/>
       <c r="F5" s="11" t="inlineStr">
         <is>
           <t>MATH 1003-001
@@ -2108,7 +2089,7 @@
       <c r="B7" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-005
-Corley 104
+Rothwell 312
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2116,7 +2097,7 @@
       <c r="D7" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-005
-Corley 104
+Rothwell 312
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2124,7 +2105,7 @@
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-005
-Corley 104
+Rothwell 312
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2147,11 +2128,41 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-001
+Corley 104
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0903-001
+Corley 104
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-001
+Corley 104
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0903-001
+Corley 104
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-001
+Corley 104
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2159,11 +2170,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -2172,9 +2183,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2288,14 +2299,14 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="14">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C3:C5"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E5"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C6:C8"/>
@@ -2372,24 +2383,24 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 2924-002
+Rothwell 206
 8:00 AM-8:50 AM</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 2924-002
+Rothwell 206
 8:00 AM-8:50 AM</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 2924-002
+Rothwell 206
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -2506,7 +2517,7 @@
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>MATH 4971-001
-Corley 101
+Rothwell 221
 11:00 AM-12:20 PM</t>
         </is>
       </c>
@@ -2517,13 +2528,7 @@
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-002
-Corley 101
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="n"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
           <t>STAT 3113-001
@@ -2541,7 +2546,7 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="n"/>
+      <c r="E10" s="4" t="n"/>
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2553,7 +2558,7 @@
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2575,7 +2580,13 @@
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Rothwell 206
+1:00 PM-2:20 PM</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
@@ -2587,7 +2598,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
@@ -2599,7 +2610,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
@@ -2667,8 +2678,8 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="15">
+    <mergeCell ref="C13:C15"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="E9:E11"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B3:B4"/>
@@ -2750,29 +2761,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2780,11 +2773,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2819,7 +2812,7 @@
       <c r="B7" s="11" t="inlineStr">
         <is>
           <t>MATH 1113-F01
-Ross Pendergraft Library 220
+Corley 269
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2827,7 +2820,7 @@
       <c r="D7" s="11" t="inlineStr">
         <is>
           <t>MATH 1113-F01
-Ross Pendergraft Library 220
+Corley 269
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2835,7 +2828,7 @@
       <c r="F7" s="11" t="inlineStr">
         <is>
           <t>MATH 1113-F01
-Ross Pendergraft Library 220
+Corley 269
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2858,41 +2851,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 1113-001
-Corley 104
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 0903-001
-Corley 104
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 1113-001
-Corley 104
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 0903-001
-Corley 104
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 1113-001
-Corley 104
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2900,11 +2863,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -2913,9 +2876,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2943,13 +2906,7 @@
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-1:00 PM-2:20 PM</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
           <t>MATH 2924-001
@@ -2979,7 +2936,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="8" t="n"/>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="6" t="n"/>
@@ -2991,7 +2948,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="4" t="n"/>
@@ -3070,25 +3027,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="18">
+  <mergeCells count="9">
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -3214,7 +3162,7 @@
       <c r="B7" s="11" t="inlineStr">
         <is>
           <t>MATH 1914-003
-Corley 268
+Corley 104
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -3222,7 +3170,7 @@
       <c r="D7" s="11" t="inlineStr">
         <is>
           <t>MATH 1914-003
-Corley 268
+Corley 104
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -3230,7 +3178,7 @@
       <c r="F7" s="11" t="inlineStr">
         <is>
           <t>MATH 1914-003
-Corley 268
+Corley 104
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -3522,11 +3470,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Corley 101
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Corley 101
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Corley 101
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3534,11 +3500,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3562,7 +3528,7 @@
       <c r="C6" s="11" t="inlineStr">
         <is>
           <t>MATH 1914-001
-Corley 101
+Corley 268
 9:30 AM-10:50 AM</t>
         </is>
       </c>
@@ -3576,26 +3542,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Corley 101
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2223-003
+Corley 103
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Corley 101
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2223-003
+Corley 103
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Corley 101
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2223-003
+Corley 103
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -3618,7 +3584,13 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Corley 103
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
           <t>MATH 2223-002
@@ -3626,7 +3598,13 @@
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Corley 103
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>MATH 2223-002
@@ -3634,7 +3612,13 @@
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Corley 103
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -3642,11 +3626,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -3678,29 +3662,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-003
-Rothwell 221
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-003
-Rothwell 221
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-003
-Rothwell 221
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -3708,11 +3674,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -3720,21 +3686,9 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1110-003
-Rothwell 221
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1110-003
-Rothwell 221
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
     </row>
@@ -3744,9 +3698,9 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
     </row>
@@ -3812,19 +3766,20 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="13">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B13:B14"/>
+  <mergeCells count="14">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B15:B16"/>
     <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3894,26 +3849,38 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1003-002
-Ross Pendergraft Library 331
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0903-002
+Corley 104
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1003-002
-Ross Pendergraft Library 331
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-002
+Corley 104
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0903-002
+Corley 104
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1003-002
-Ross Pendergraft Library 331
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-002
+Corley 104
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0903-002
+Corley 104
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -3925,9 +3892,9 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="8" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="8" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3943,7 +3910,7 @@
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>MATH 0803-002
@@ -3951,7 +3918,7 @@
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
+      <c r="E5" s="6" t="n"/>
       <c r="F5" s="11" t="inlineStr">
         <is>
           <t>MATH 0803-002
@@ -3978,26 +3945,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2223-003
-Corley 103
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1003-002
+Ross Pendergraft Library 331
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2223-003
-Corley 103
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1003-002
+Ross Pendergraft Library 331
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2223-003
-Corley 103
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1003-002
+Ross Pendergraft Library 331
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -4020,29 +3987,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Corley 103
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Corley 103
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Corley 103
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -4050,11 +3999,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -4086,26 +4035,26 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2243-001
-Corley 104
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1113-003
+Rothwell 221
 1:00 PM-1:50 PM</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2243-001
-Corley 104
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1113-003
+Rothwell 221
 1:00 PM-1:50 PM</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2243-001
-Corley 104
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1113-003
+Rothwell 221
 1:00 PM-1:50 PM</t>
         </is>
       </c>
@@ -4128,9 +4077,21 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1110-003
+Rothwell 221
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1110-003
+Rothwell 221
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
     </row>
@@ -4140,9 +4101,9 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
     </row>
@@ -4196,22 +4157,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="D15:D16"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4374,7 +4336,7 @@
       <c r="B9" s="7" t="inlineStr">
         <is>
           <t>STAT 3153-002
-Corley 102
+Corley 269
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -4382,7 +4344,7 @@
       <c r="D9" s="7" t="inlineStr">
         <is>
           <t>STAT 3153-002
-Corley 102
+Corley 269
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -4390,7 +4352,7 @@
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>STAT 3153-002
-Corley 102
+Corley 269
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -4583,7 +4545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4711,11 +4673,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2703-001
+Corley 101
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2703-001
+Corley 101
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2703-001
+Corley 101
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4723,11 +4703,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -4735,11 +4715,41 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-002
+Corley 101
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
+Corley 101
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-002
+Corley 101
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
+Corley 101
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-002
+Corley 101
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -4747,11 +4757,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -4760,9 +4770,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4783,17 +4793,17 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-002
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
 Corley 101
 1:00 PM-1:50 PM</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-002
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
 Corley 101
 1:00 PM-1:50 PM</t>
         </is>
@@ -4805,9 +4815,9 @@
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-002
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
 Corley 101
 1:00 PM-1:50 PM</t>
         </is>
@@ -4921,35 +4931,30 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Online / TBA</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>MATH 2703-TC1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="14">
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:D16"/>
+  <mergeCells count="21">
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="E16:E18"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E6:E8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -5299,6 +5304,389 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Instructor Schedule -- Limperis, Thomas G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Rothwell 212
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Rothwell 212
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Rothwell 212
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 206
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 306
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 306
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 306
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 102
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 102
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 268
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 102
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Corley 268
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Corley 268
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Corley 268
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F20"/>
+  <mergeCells count="15">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E6:E8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5313,7 +5701,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Instructor Schedule -- Limperis, Thomas G.</t>
+          <t>Instructor Schedule -- Overduin, Matthew D.</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5780,18 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2243-002
+Ross Pendergraft Library 220
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 206
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2243-002
+Ross Pendergraft Library 220
 9:30 AM-10:50 AM</t>
         </is>
       </c>
@@ -5409,29 +5803,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 306
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 306
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 306
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -5439,11 +5815,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="4" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -5451,41 +5827,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2703-001
-Corley 101
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Rothwell 206
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2703-001
-Corley 101
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Rothwell 206
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2703-001
-Corley 101
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -5493,11 +5839,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -5506,9 +5852,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -5529,11 +5875,29 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2243-001
+Corley 104
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2243-001
+Corley 104
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2243-001
+Corley 104
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -5541,11 +5905,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
+      <c r="B14" s="6" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -5553,11 +5917,29 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3123-001
+Corley 102
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3123-001
+Corley 102
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3123-001
+Corley 102
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -5565,11 +5947,11 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -5627,388 +6009,25 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>MATH 4993-001</t>
+          <t>MATH 2703-TC1</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="11">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
+  <mergeCells count="10">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="E6:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Instructor Schedule -- Overduin, Matthew D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Corley 268
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Corley 268
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Corley 268
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>8:30 AM</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Rothwell 212
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Rothwell 212
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Rothwell 212
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>9:30 AM</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2243-002
-Ross Pendergraft Library 220
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2243-002
-Ross Pendergraft Library 220
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>10:30 AM</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>11:00 AM</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>11:30 AM</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>12:30 PM</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>1:30 PM</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2:00 PM</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>MATH 3123-001
-Corley 102
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>MATH 3123-001
-Corley 102
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>MATH 3123-001
-Corley 102
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2:30 PM</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>3:30 PM</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>4:30 PM</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:F20"/>
-  <mergeCells count="12">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D5:D6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>